--- a/medford_sektornye_fazirovannye_datchiki_uzi.xlsx
+++ b/medford_sektornye_fazirovannye_datchiki_uzi.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Секторные фазированные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов GE, Siemens, Mindray, Samsung, Canon, SonoScape, Chison — всего 20 позиций.</t>
+          <t>Секторные фазированные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов GE, Siemens, Mindray, Samsung, Canon, SonoScape, Chison.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_sektornye_fazirovannye_datchiki_uzi.xlsx
+++ b/medford_sektornye_fazirovannye_datchiki_uzi.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать секторные фазированные датчики УЗИ для клиники?</t>
+          <t>Что такое секторный фазированный датчик?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Количество элементов, Диапазон частот, МГц, Размер апертуры, мм, Радиус кривизны, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Это ультразвуковой датчик с малой контактной поверхностью и электронным (фазированным) управлением лучом за счёт задержек сигналов на множестве мелких пьезоэлементов, без механического движения. Он даёт веерообразное поле, расширяющееся вглубь, и позволяет сканировать через узкие анатомические окна — межреберья, родничок, височную кость.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Для каких исследований он нужен?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Основные применения — эхокардиография (осмотр сердца взрослых и детей через межреберья), транскраниальные исследования (через родничок у новорождённых или височное окно у взрослых) и экстренная медицина по FAST-протоколам. Малая апертура и большая глубина проникновения делают его основным датчиком в кардиологии.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Как понять, подойдёт ли датчик к моему аппарату?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены GE, Siemens, Mindray, Samsung, Canon, SonoScape, Chison. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Совместимость определяют бренд, модель, поколение сканера и тип разъёма. Датчик рассчитан на свою линейку аппаратов: GE — к GE, Mindray — к Mindray, Siemens — к Siemens. Сообщите точную марку и модель вашего УЗИ-аппарата, и мы сверим совместимость по разъёму до покупки.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какую частоту выбрать?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Низкие частоты (1–5 МГц) дают большую глубину проникновения — до 20–30 см — и подходят для сердца взрослых и брюшной полости. Более высокие частоты улучшают детализацию поверхностных структур и применяются в педиатрии. В каталоге диапазоны от 1 до 9,9 МГц; выбор под пациента и задачу определяет врач.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Чем монокристаллический датчик лучше обычного?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Монокристаллические (single crystal) преобразователи дают более чистый сигнал, шире динамический диапазон и лучшее соотношение сигнал/шум по сравнению с обычной пьезокерамикой. Это заметно в кардиологической картинке. В каталоге есть такие модели: Mindray SP5-1N, SP5-1s и Samsung PM1-6A.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что такое секторный датчик УЗИ?</t>
+          <t>Нужно ли РУ на датчик УЗИ?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Да. Датчик УЗИ — медицинское изделие, для легального применения нужно действующее регистрационное удостоверение Росздравнадзора, как правило в составе регистрации аппарата или датчика. Наличие и реквизиты РУ уточняйте до покупки; без него датчик нельзя использовать в лицензируемой диагностике.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какие существуют типы датчиков для УЗИ?</t>
+          <t>Даёте ли гарантию на датчики, в том числе восстановленные?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>На поставляемые датчики распространяется гарантия, а проверку и ремонт выполняет собственный инженерный сервис. Для восстановленных датчиков предоставляется информация об объёме работ и результатах тестирования элементов. Условия, срок гарантии и порядок обращения по конкретной позиции уточняйте у менеджера при оформлении.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Секторные фазированные датчики УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов GE, Siemens, Mindray, Samsung, Canon, SonoScape, Chison.</t>
+          <t>Секторные фазированные датчики УЗИ — это ультразвуковые преобразователи с малой рабочей поверхностью и электронным управлением лучом для сканирования через узкие анатомические окна. В каталоге представлены датчики GE (S4-10-D, 3SC-RS), Siemens (P4-2, 4V1, 8V4, 10V4), Mindray (SP5-1N, SP5-1s, P4-2s), Canon (PST-30BT, PST-50BT), Samsung (PM1-6A), SonoScape (3P-A), Chison и SIUI. Число элементов — от 64 до 288, диапазон частот — от 1 до 9,9 МГц. Низкочастотные модели дают большую глубину для эхокардиографии.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Секторные датчики по применению и частоте</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое секторные фазированные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4520,251 +4520,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Секторные датчики по применению и частоте</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Применение</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Частотный диапазон</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Количество элементов</t>
+          <t>Особенность</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Диапазон частот, МГц</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Размер апертуры, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Радиус кривизны, мм</t>
+          <t>Пример моделей</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Секторный фазированный датчик GE S4-10-D</t>
+          <t>Эхокардиография взрослых</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>Низкий (1–5 МГц)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>Большая глубина проникновения</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3-9</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mindray SP5-1N, Canon PST-30BT, Siemens 4V1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Siemens 10V4 секторный датчик УЗИ</t>
+          <t>Педиатрия / поверхностные</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Выше (до 8–10 МГц)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>Лучшая детализация</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>4,1-9,9</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>13.056</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Siemens 8V4, GE S4-10-D, Siemens 10V4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Секторный фазированный монокристаллический датчик Mindray SP5-1N</t>
+          <t>Монокристаллические</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>1–6 МГц</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>Чистый сигнал, широкий динамический диапазон</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1,0-5,0</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Siemens 4V1C секторный датчик УЗИ</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>1-4,5</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Siemens 4V1 секторный датчик УЗИ</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>1-4</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Секторный фазированный матричный монокристальный датчик Samsung PM1-6A</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>1-6</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mindray SP5-1s, Samsung PM1-6A</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4776,7 +4638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5102,12 +4964,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Проверьте совместимость с аппаратом</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается секторные фазированные датчики УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Датчик подбирают под конкретный УЗИ-сканер: важны бренд, модель, поколение и тип разъёма. Датчик GE подойдёт к аппаратам GE, Mindray — к Mindray и так далее. До покупки сообщите марку и модель аппарата — это первое условие, без совпадения разъёма датчик работать не будет.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5147,12 +5009,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Определите область исследования</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Секторные фазированные датчики применяют в эхокардиографии (осмотр сердца через межреберья), транскраниальных исследованиях (через родничок или височное окно) и экстренной медицине по FAST-протоколам. От области зависят требования к частоте и глубине. Кардиология взрослых требует хорошей глубины проникновения.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5192,12 +5054,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Подберите диапазон частот</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Количество элементов, Диапазон частот, МГц, Размер апертуры, мм, Радиус кривизны, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Частота определяет глубину и детализацию: низкие частоты (1–5 МГц) дают большую глубину для сердца взрослых и брюшной полости, более высокие — лучшую детализацию поверхностных структур и подходят для педиатрии. В каталоге диапазоны от 1 до 9,9 МГц. Выбирайте под пациента и задачу.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5237,12 +5099,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените число элементов и апертуру</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: GE, Siemens, Mindray, Samsung, Canon, SonoScape, Chison.</t>
+          <t>Число элементов в каталоге — от 64 до 288. Больше элементов и подходящая апертура улучшают формирование луча и качество картинки. Например, у Siemens 4P1 — 288 элементов. Сопоставьте эти параметры с классом аппарата и требованиями к изображению.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5282,12 +5144,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Рассмотрите монокристаллические матричные версии</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Монокристаллические (single crystal) датчики — Mindray SP5-1N и SP5-1s, Samsung PM1-6A — дают более чистый сигнал и широкий динамический диапазон по сравнению с обычной пьезокерамикой. Если важно качество кардиологической картинки, рассмотрите такие модели при совместимости с аппаратом.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5327,12 +5189,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните состояние, РУ и гарантию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Проверьте состояние датчика: целостность кабеля, линзы и разъёма, отсутствие «мёртвых» элементов, влияющих на картинку. Датчик — медицинское изделие, уточните действующее РУ Росздравнадзора и условия гарантии. Для восстановленных датчиков запросите объём проведённых работ и результаты тестирования элементов, чтобы понимать реальное качество перед покупкой.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5382,7 +5244,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Секторные фазированные датчики УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены GE, Siemens, Mindray, Samsung, Canon, SonoScape, Chison. При выборе обращают внимание на количество элементов, диапазон частот, размер апертуры, радиус кривизны, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Секторный фазированный датчик выбирают в первую очередь по аппарату: бренд, разъём и поколение сканера определяют совместимость, и это я проверяю до сделки. Для кардиологии взрослых берут низкочастотные модели около 1–5 МГц с хорошей глубиной, для педиатрии и поверхностных задач — версии повыше по частоте. Монокристаллические матричные датчики дают более чистый сигнал. Число элементов и апертуру сопоставляю с задачами исследования.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5666,13 +5528,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое секторные фазированные датчики УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Секторные фазированные датчики УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов GE, Siemens, Mindray, Samsung, Canon, SonoScape, Chison. Подберём вариант под задачи вашего отделения.</t>
+          <t>Секторный фазированный датчик УЗИ — преобразователь с малой контактной поверхностью и электронным управлением лучом для сканирования через узкие окна: межреберья, родничок, височную кость. Веерообразное поле и низкие частоты (обычно 1–5 МГц) дают большую глубину проникновения, до 20–30 см. Основные применения — эхокардиография, транскраниальные и экстренные FAST-исследования. Ключевые параметры выбора: число элементов (в каталоге 64–288), диапазон частот и совместимость с конкретным УЗИ-аппаратом по бренду, разъёму и модели. Есть монокристаллические матричные версии для кардиологии.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5709,13 +5571,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое секторный фазированный датчик</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Количество элементов, Диапазон частот, МГц, Размер апертуры, мм, Радиус кривизны, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Секторный фазированный датчик УЗИ — преобразователь с малой рабочей поверхностью и электронным управлением лучом. Луч отклоняется за счёт изменения задержек сигналов на множестве мелких пьезоэлементов, без механического движения. Датчик формирует веерообразное поле, расширяющееся от узкого основания вглубь, что позволяет сканировать через узкие анатомические окна.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5752,13 +5614,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Области применения</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Основные сценарии — эхокардиография (осмотр сердца через межреберные промежутки), транскраниальные исследования (через родничок у новорождённых или височное окно у взрослых) и экстренная медицина по FAST-протоколам в реанимации и на скорой. Низкая частота обеспечивает большую глубину проникновения, а малая апертура — доступ через узкие окна.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5795,13 +5657,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Характеристики при выборе</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Ключевые параметры: диапазон частот (в каталоге 1–9,9 МГц; ниже — глубже, выше — детальнее), число элементов (64–288), тип преобразователя (обычная керамика или монокристалл) и апертура. Определяющим остаётся совместимость с аппаратом по бренду, модели и разъёму — без совпадения датчик не подключить.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5818,6 +5680,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Бренды и модели в каталоге</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Каталог включает секторные фазированные датчики GE (S4-10-D, 3SC-RS), Siemens (P4-2, 4V1, 4V1C, 8V4, 10V4, 4P1, P8-4), Mindray (SP5-1N, SP5-1s, P4-2s), Canon (PST-25BT, PST-30BT, PST-50BT, PSU-30BT), Samsung PM1-6A, SonoScape 3P-A, Chison D3P64L и SIUI P5FN. Есть монокристаллические матричные версии для кардиологии.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>sektornye_fazirovannye_datchiki_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
